--- a/src/Excelsior.Tests/TemplateSheetTests.DateRange.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.DateRange.verified.xlsx
@@ -84,7 +84,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="date" operator="between" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be a date between 2020-01-01 and 2030-12-31." sqref="B2:B26">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a date between 2020-01-01 and 2030-12-31." prompt="Enter a date between 2020-01-01 and 2030-12-31." sqref="B2:B26">
       <formula1>43831</formula1>
       <formula2>47848</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/TemplateSheetTests.DateRange.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.DateRange.verified.xlsx
@@ -84,7 +84,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a date between 2020-01-01 and 2030-12-31." prompt="Enter a date between 2020-01-01 and 2030-12-31." sqref="B2:B26">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a date between 2020-01-01 and 2030-12-31." prompt="Date between 2020-01-01 and 2030-12-31" sqref="B2:B26">
       <formula1>43831</formula1>
       <formula2>47848</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/TemplateSheetTests.DateRange.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.DateRange.verified.xlsx
@@ -84,7 +84,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="date" operator="between" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be a date between 2020-01-01 and 2030-12-31." sqref="B2:B26">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a date between 2020-01-01 and 2030-12-31." prompt="Date between 2020-01-01 and 2030-12-31" sqref="B2:B26">
       <formula1>43831</formula1>
       <formula2>47848</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/TemplateSheetTests.DateRange.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.DateRange.verified.xlsx
@@ -93,7 +93,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="Hires">
     <column index="1" property="Name"/>
     <column index="2" property="HireDate"/>
